--- a/data/trans_orig/IP05A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A02-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54371</t>
+          <t>54896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68879</t>
+          <t>69013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52170</t>
+          <t>52723</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65975</t>
+          <t>66368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111786</t>
+          <t>111694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131781</t>
+          <t>131775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>15968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>29211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>33992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53015</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>17745</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>288388</t>
+          <t>288126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>318124</t>
+          <t>317973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356766</t>
+          <t>357291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>386185</t>
+          <t>386201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>654204</t>
+          <t>655783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>697757</t>
+          <t>696603</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75267</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101880</t>
+          <t>103251</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69328</t>
+          <t>70097</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96439</t>
+          <t>96169</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>153262</t>
+          <t>152423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190960</t>
+          <t>190409</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31340</t>
+          <t>31816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28871</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33978</t>
+          <t>34442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>55150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131801</t>
+          <t>132872</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149392</t>
+          <t>149087</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120112</t>
+          <t>119255</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>136408</t>
+          <t>134893</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257364</t>
+          <t>256636</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>280369</t>
+          <t>279980</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36518</t>
+          <t>36651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17293</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>32887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42784</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63912</t>
+          <t>63896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>16133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>489795</t>
+          <t>489259</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>526722</t>
+          <t>524523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>541869</t>
+          <t>541278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>577582</t>
+          <t>576365</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1042627</t>
+          <t>1041096</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1093677</t>
+          <t>1091019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122278</t>
+          <t>122655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157524</t>
+          <t>155323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111948</t>
+          <t>113705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145141</t>
+          <t>148353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>242381</t>
+          <t>245220</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292513</t>
+          <t>291537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42615</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>23911</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41160</t>
+          <t>41252</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52940</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78094</t>
+          <t>78249</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70067</t>
+          <t>70398</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82025</t>
+          <t>82089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64026</t>
+          <t>64097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75619</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138763</t>
+          <t>139261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155560</t>
+          <t>155093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17864</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33188</t>
+          <t>33205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369573</t>
+          <t>369314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395221</t>
+          <t>396028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>408524</t>
+          <t>407423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>433720</t>
+          <t>433421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>787198</t>
+          <t>784534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>825472</t>
+          <t>821771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45457</t>
+          <t>44738</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67814</t>
+          <t>68624</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47237</t>
+          <t>47090</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70397</t>
+          <t>70233</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>98019</t>
+          <t>99254</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>130953</t>
+          <t>133232</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37015</t>
+          <t>35835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123497</t>
+          <t>123556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>140287</t>
+          <t>140135</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>131256</t>
+          <t>130112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148734</t>
+          <t>148235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>260153</t>
+          <t>260515</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>283990</t>
+          <t>284274</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>33041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18559</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34218</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40027</t>
+          <t>40015</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61509</t>
+          <t>61377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>575208</t>
+          <t>576110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>608876</t>
+          <t>608635</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>616820</t>
+          <t>614993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>650299</t>
+          <t>649340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1202781</t>
+          <t>1201354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1249352</t>
+          <t>1247580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77248</t>
+          <t>78182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107794</t>
+          <t>108026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81498</t>
+          <t>81202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112013</t>
+          <t>112257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168303</t>
+          <t>168976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210014</t>
+          <t>210088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>34987</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31251</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>37966</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59623</t>
+          <t>60840</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47508</t>
+          <t>48177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55813</t>
+          <t>56075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52655</t>
+          <t>52412</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62199</t>
+          <t>62138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102873</t>
+          <t>103535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116186</t>
+          <t>116444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400085</t>
+          <t>400259</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423096</t>
+          <t>423457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>413429</t>
+          <t>412295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>437725</t>
+          <t>437026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>820224</t>
+          <t>819642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>854550</t>
+          <t>854352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33170</t>
+          <t>34060</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54444</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62685</t>
+          <t>62275</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79891</t>
+          <t>79439</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109343</t>
+          <t>109482</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18994</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36113</t>
+          <t>36019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139681</t>
+          <t>139738</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154769</t>
+          <t>154403</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164066</t>
+          <t>163110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176778</t>
+          <t>176457</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>308288</t>
+          <t>308017</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327915</t>
+          <t>327908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>27312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19966</t>
+          <t>20682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>24887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>596995</t>
+          <t>599072</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>626683</t>
+          <t>627971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638895</t>
+          <t>641013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>668563</t>
+          <t>668334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1246679</t>
+          <t>1246999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1290319</t>
+          <t>1289294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57032</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84465</t>
+          <t>81362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>61891</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>88419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123801</t>
+          <t>124140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>162698</t>
+          <t>161926</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29274</t>
+          <t>28829</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48265</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52093</t>
+          <t>52071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44701</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56130</t>
+          <t>56226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93125</t>
+          <t>93304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106297</t>
+          <t>106500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>307612</t>
+          <t>317045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>424216</t>
+          <t>423613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462724</t>
+          <t>464049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486384</t>
+          <t>486984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>786809</t>
+          <t>779996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>902339</t>
+          <t>902326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>149693</t>
+          <t>138211</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40432</t>
+          <t>41154</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>58964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>174195</t>
+          <t>199326</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24720</t>
+          <t>24462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128602</t>
+          <t>128350</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>140640</t>
+          <t>140918</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146872</t>
+          <t>147738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>167470</t>
+          <t>168629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>281940</t>
+          <t>282100</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>305536</t>
+          <t>305286</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17694</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>40132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>16123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>506069</t>
+          <t>498731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>609467</t>
+          <t>609546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>671444</t>
+          <t>669819</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>703641</t>
+          <t>702991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1183095</t>
+          <t>1190782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1300444</t>
+          <t>1302075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145553</t>
+          <t>153373</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67091</t>
+          <t>69011</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88985</t>
+          <t>88332</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210298</t>
+          <t>201352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27484</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>48426</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A02-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60058</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52683</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66351</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>62353</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54896</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69013</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>55320</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>69308</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>69,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>60058</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52723</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66368</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>69,15%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111694</t>
+          <t>112648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131775</t>
+          <t>131644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21438</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15305</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28082</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21802</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15968</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29211</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15598</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28816</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>24,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21438</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15375</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28501</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>34475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53913</t>
+          <t>52407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5350</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9820</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6185</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3329</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10615</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3179</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10969</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,85%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5350</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2587</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9867</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>17174</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>371569</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>355543</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>385157</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>461</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>304512</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>288126</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>317973</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>289322</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>319193</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>73,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>371569</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>357291</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>386201</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>78,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655783</t>
+          <t>654431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>696603</t>
+          <t>694645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82713</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>69577</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>95691</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>88178</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>74974</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>103251</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>74993</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>102443</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>21,23%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>18,05%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>24,85%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82713</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>70097</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96169</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>14,76%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>152423</t>
+          <t>152632</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190409</t>
+          <t>189910</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20669</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14779</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28961</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>22732</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16301</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31816</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16346</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>31488</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,47%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20669</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14202</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28432</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34442</t>
+          <t>33669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55150</t>
+          <t>54644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>474951</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>474951</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>474951</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>415422</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>415422</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>415422</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>474951</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>474951</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>474951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>128202</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>119031</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>135211</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>81,07%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>75,27%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>85,5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>141004</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>132872</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149087</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>132303</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>148122</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>81,21%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>76,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>85,87%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>128202</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>119255</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>134893</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>81,07%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>256636</t>
+          <t>257414</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>279980</t>
+          <t>280819</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18390</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33435</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28306</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21244</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36651</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21602</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>38514</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>16,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18161</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>32887</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42391</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63896</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -1861,107 +1861,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2642</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10691</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4309</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8399</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8579</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5435</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2561</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10993</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>9745</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>5361</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>16394</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>9745</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>5580</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>16133</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173619</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173619</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173619</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>559828</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>542207</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>576577</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>77,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>75,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>80,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>759</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>507869</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>489259</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>524523</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>487958</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>525268</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>74,75%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>72,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>559828</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>541278</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>576365</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>77,76%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1041096</t>
+          <t>1043592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1091019</t>
+          <t>1093227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>128652</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>113627</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>146104</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>138287</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>122655</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>155323</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>121840</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>158953</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>20,35%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>128652</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>113705</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>148353</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>17,87%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245220</t>
+          <t>242996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>291537</t>
+          <t>288054</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31454</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23613</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>40211</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>33226</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>24933</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>42816</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>24466</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>43858</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,89%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>31454</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23911</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>41252</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>52266</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78249</t>
+          <t>77957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>719934</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>719934</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>719934</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>679381</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>679381</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>679381</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>719934</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>719934</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>719934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>70741</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64094</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75798</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>77101</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>70398</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>82089</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>71028</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>82739</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>84,17%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>76,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>70741</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>64097</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>76109</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>82,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139261</t>
+          <t>138847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155093</t>
+          <t>155416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8246</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19150</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11689</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7254</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17887</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6815</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17770</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>12,76%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12863</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8098</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19302</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33205</t>
+          <t>32395</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -3009,67 +3009,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6340</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>2811</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7096</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6002</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>422369</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>409368</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>435905</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>556</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>383072</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>369314</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>396028</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>369322</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>395091</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>81,67%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>422369</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>407423</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>433421</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,42%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>82,4%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>784534</t>
+          <t>787876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821771</t>
+          <t>821450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58114</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>46931</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>69910</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11,75%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>56126</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44738</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>68624</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>44928</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>68694</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>12,41%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>58114</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47090</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>70233</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>99254</t>
+          <t>98766</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133232</t>
+          <t>132278</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -3465,67 +3465,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>13963</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8824</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21485</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>13012</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8175</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20662</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7695</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19955</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,88%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13963</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8968</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21954</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35835</t>
+          <t>36434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>140518</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132198</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>148578</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>81,59%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>76,76%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>86,27%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>132488</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>123556</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>140135</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>122773</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>139861</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>79,42%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>74,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>84,01%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>140518</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>130112</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>148235</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>81,59%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>260515</t>
+          <t>261336</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>284274</t>
+          <t>285423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -3808,67 +3808,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>25416</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18319</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32870</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>24796</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18206</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33041</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18247</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33946</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>14,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25416</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18907</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>35519</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,76%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40015</t>
+          <t>39752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61377</t>
+          <t>61608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6294</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2749</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11599</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>9527</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5221</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>15350</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15665</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6294</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2749</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>12327</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>633628</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>615619</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>649537</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>84,16%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>855</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>592662</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>576110</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>608635</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>576199</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>608833</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>83,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>81,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>85,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>633628</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>614993</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>649340</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>84,16%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1201354</t>
+          <t>1202424</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1247580</t>
+          <t>1250882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>96392</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>81929</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>112245</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>92612</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>78182</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>108026</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>78493</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>107391</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>13,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>96392</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>81202</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>112257</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168976</t>
+          <t>167665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210088</t>
+          <t>209165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22845</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15401</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31971</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>25350</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18133</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34987</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17707</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>34639</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,57%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>22845</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>16153</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>32102</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37966</t>
+          <t>38332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60840</t>
+          <t>63330</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>710623</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>710623</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>710623</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57840</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52246</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>62345</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,14%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>52517</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48177</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>56075</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>47618</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>55717</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>88,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>57840</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52412</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>62138</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>84,3%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103535</t>
+          <t>102031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116444</t>
+          <t>115467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -4946,72 +4946,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10074</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5586</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15745</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6204</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2827</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10383</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3306</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11254</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10074</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5808</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15700</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -5064,102 +5064,102 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3930</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>657</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3430</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2910</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4694</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1357</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>4424</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>425964</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>412343</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>436975</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>624</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>412538</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>400259</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>423457</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>401123</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>423303</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>87,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>425964</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>412295</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>437026</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,16%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>819642</t>
+          <t>822020</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>854352</t>
+          <t>855244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50604</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>62772</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12,84%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43166</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34060</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>54133</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>34382</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>54001</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50604</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>40376</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>62275</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79439</t>
+          <t>78986</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109482</t>
+          <t>107876</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -5515,107 +5515,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12167</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6929</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19120</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14848</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9643</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21783</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22375</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>27015</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>19692</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>36266</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12167</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7346</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18559</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>27015</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>19615</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>36019</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>470552</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>470552</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>470552</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>170683</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>162661</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>176604</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>91,03%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>94,19%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148022</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>139738</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>154403</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>139474</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>154483</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>85,71%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>80,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>89,4%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>170683</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>163110</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>176457</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>308017</t>
+          <t>307509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327908</t>
+          <t>327591</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13874</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8656</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20854</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19568</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13650</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27312</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13444</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27072</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13874</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8639</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20682</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43422</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8047</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5112</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2238</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9864</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2378</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9483</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2938</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7997</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>654487</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>639390</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>668324</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>87,87%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>85,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>924</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>613077</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>599072</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>627971</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>598403</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>626252</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>87,25%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>85,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>654487</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>641013</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>668334</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1246999</t>
+          <t>1246449</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1289294</t>
+          <t>1287092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>74552</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>61279</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>88321</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>68939</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>55672</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>81362</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>57023</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>81687</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>74552</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>61891</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>88419</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124140</t>
+          <t>126534</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>161926</t>
+          <t>162143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15805</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9783</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23637</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>20617</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14189</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28829</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13866</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>29414</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2,93%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>15805</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>10271</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>23076</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27240</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48086</t>
+          <t>47984</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>702633</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>702633</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>702633</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47073</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41215</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51368</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>72,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>49048</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>44022</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52071</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,7%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>80,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51772</t>
+          <t>41038</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44982</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56226</t>
+          <t>44079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>100820</t>
+          <t>88112</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93304</t>
+          <t>80338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106500</t>
+          <t>93173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2675</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7122</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4258</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1636</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3158</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6895</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6984</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3126</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12882</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1461</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8561</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>437749</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>427036</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>448007</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>588</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>396535</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>317045</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>423613</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>476204</t>
+          <t>392180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464049</t>
+          <t>380584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486984</t>
+          <t>402217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>872739</t>
+          <t>829929</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>779996</t>
+          <t>813696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>902326</t>
+          <t>843311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>27471</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19216</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>37542</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58164</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30406</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>138211</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>30,01%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>34369</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>25136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41154</t>
+          <t>45577</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>87668</t>
+          <t>61840</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58964</t>
+          <t>49729</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>199326</t>
+          <t>76951</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10458</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17257</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5811</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2765</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10583</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>16357</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149120</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140591</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155447</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>89,05%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>83,95%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>135672</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>128350</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>140918</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>85,82%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>159836</t>
+          <t>135572</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>147738</t>
+          <t>128080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>168629</t>
+          <t>141039</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>295509</t>
+          <t>284692</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>282100</t>
+          <t>274294</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>305286</t>
+          <t>293276</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14289</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8607</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21521</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8374</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14604</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>32818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4053</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1628</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5505</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2569</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9961</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>633942</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>616644</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>646519</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>90,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>856</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>581254</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>498731</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>609546</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>87,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>75,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>884</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>687812</t>
+          <t>568791</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>669819</t>
+          <t>554446</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>702991</t>
+          <t>581093</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1269068</t>
+          <t>1202733</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1190782</t>
+          <t>1183048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1302075</t>
+          <t>1220951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>89,01%</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>83,52%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44435</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>35468</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>59394</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>68057</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>39850</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>153373</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51178</t>
+          <t>45089</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38996</t>
+          <t>34729</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69011</t>
+          <t>59653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>119235</t>
+          <t>89524</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88332</t>
+          <t>74130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>201352</t>
+          <t>108250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>21495</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14296</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>30609</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>15427</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9891</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23244</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31694</t>
+          <t>23046</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>37465</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28003</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48426</t>
+          <t>48454</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
